--- a/mode_docx_gen/pmi_tokz/part/lvarctoc/ptoc1/PTOC1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/lvarctoc/ptoc1/PTOC1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\12. ТК ЗДЗ 35\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\lvarctoc\ptoc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="89">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -266,6 +266,27 @@
   </si>
   <si>
     <t>Токовый орган пуска дуговой защиты</t>
+  </si>
+  <si>
+    <t>SGF2</t>
+  </si>
+  <si>
+    <t>INT32</t>
+  </si>
+  <si>
+    <t>Выбор пускового органа</t>
+  </si>
+  <si>
+    <t>Выбор_пуск</t>
+  </si>
+  <si>
+    <t>0 - Внутренний, 1 - МТЗ 1 ст, 2 - МТЗ 2 ст, 3 - МТЗ 3 ст</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Iset</t>
   </si>
 </sst>
 </file>
@@ -288,7 +309,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,8 +328,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -344,11 +371,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -359,6 +397,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -661,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -669,13 +711,13 @@
     <col min="3" max="3" width="51.7109375" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="20.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="75.42578125" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" customWidth="1"/>
     <col min="27" max="27" width="14.28515625" customWidth="1"/>
     <col min="28" max="28" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -766,8 +808,11 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -859,7 +904,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -951,7 +996,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1043,7 +1088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
@@ -1135,7 +1180,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -1227,7 +1272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1319,7 +1364,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1408,6 +1453,101 @@
         <v>32</v>
       </c>
       <c r="AD8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>3</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6">
+        <v>0</v>
+      </c>
+      <c r="W9" s="6">
+        <v>0</v>
+      </c>
+      <c r="X9" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9" s="6" t="s">
         <v>32</v>
       </c>
     </row>
